--- a/Load_Test_Report_100_Users.xlsx
+++ b/Load_Test_Report_100_Users.xlsx
@@ -568,7 +568,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-08-27 10:47:03</t>
+          <t>Execution Date: 2026-08-27 11:55:39</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>32 req/sec</t>
+          <t>65 req/sec</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Your API is handling about 32 requests every second continuously.</t>
+          <t>Your API is handling about 65 requests every second continuously.</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>1450 ms</t>
+          <t>1439 ms</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>12 ms</t>
+          <t>9 ms</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>8008 ms</t>
+          <t>8007 ms</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>8040 ms</t>
+          <t>8020 ms</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>8044 ms</t>
+          <t>8027 ms</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>8059 ms (8.06s)</t>
+          <t>8036 ms (8.04s)</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>1,934 requests</t>
+          <t>3,900 requests</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>4.14 MB</t>
+          <t>8.79 MB</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="K2" s="12" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="K3" s="13" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L3" s="13" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="K4" s="12" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="K6" s="12" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="K8" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="K10" s="12" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="K12" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="K14" s="12" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="K16" s="12" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="K17" s="13" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="K18" s="12" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="K20" s="12" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="K22" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="K24" s="12" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="K25" s="13" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="L25" s="13" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="K26" s="12" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="K27" s="13" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="K28" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="K29" s="13" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="K30" s="12" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="K31" s="13" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="K32" s="12" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="K33" s="13" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="K34" s="12" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="K35" s="13" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="K36" s="12" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="K38" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="K39" s="13" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L39" s="13" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="K40" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="K41" s="13" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L41" s="13" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="K42" s="12" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="K43" s="13" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="K44" s="12" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="K45" s="13" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="K46" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="K47" s="13" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="L47" s="13" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="K48" s="12" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="K49" s="13" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="L49" s="13" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="K51" s="13" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L51" s="13" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="K52" s="12" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="L52" s="12" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="K53" s="13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L53" s="13" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="K54" s="12" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="L54" s="12" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="K55" s="13" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="L55" s="13" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="K56" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L56" s="12" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="K57" s="13" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L57" s="13" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="K58" s="12" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="L58" s="12" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="K59" s="13" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L59" s="13" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="K60" s="12" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L60" s="12" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="K61" s="13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L61" s="13" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="K62" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L62" s="12" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="K63" s="13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L63" s="13" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="K64" s="12" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="L64" s="12" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="K65" s="13" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="L65" s="13" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="K66" s="12" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L66" s="12" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="K67" s="13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L67" s="13" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="K68" s="12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L68" s="12" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="K69" s="13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L69" s="13" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="K70" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L70" s="12" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="K71" s="13" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L71" s="13" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="K72" s="12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="L72" s="12" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="K73" s="13" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L73" s="13" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="K74" s="12" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="L74" s="12" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="K75" s="13" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L75" s="13" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="K76" s="12" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="L76" s="12" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         </is>
       </c>
       <c r="K77" s="13" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L77" s="13" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="K78" s="12" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="L78" s="12" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="K79" s="13" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L79" s="13" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="K81" s="13" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="L81" s="13" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="K82" s="12" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="L82" s="12" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="K83" s="13" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="L83" s="13" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="K84" s="12" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="L84" s="12" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="K85" s="13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L85" s="13" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="K86" s="12" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="L86" s="12" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="K87" s="13" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="L87" s="13" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="K88" s="12" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L88" s="12" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="K89" s="13" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="L89" s="13" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="K90" s="12" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="L90" s="12" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="K91" s="13" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="L91" s="13" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="K92" s="12" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="L92" s="12" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="K93" s="13" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="L93" s="13" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="K94" s="12" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="L94" s="12" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         </is>
       </c>
       <c r="K95" s="13" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L95" s="13" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="K96" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L96" s="12" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="K97" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L97" s="13" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="K98" s="12" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L98" s="12" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         </is>
       </c>
       <c r="K99" s="13" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L99" s="13" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="K100" s="12" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L100" s="12" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="K101" s="13" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="L101" s="13" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="K102" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="L102" s="12" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="K103" s="13" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L103" s="13" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="K104" s="12" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="L104" s="12" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="K105" s="13" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L105" s="13" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="K106" s="12" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="L106" s="12" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="K107" s="13" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="L107" s="13" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="K108" s="12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L108" s="12" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="K109" s="13" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="L109" s="13" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="K110" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L110" s="12" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="K111" s="13" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="L111" s="13" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="K112" s="12" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="L112" s="12" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="K113" s="13" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="L113" s="13" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="K114" s="12" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="L114" s="12" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="K115" s="13" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L115" s="13" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="K116" s="12" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L116" s="12" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="K117" s="13" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L117" s="13" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="K118" s="12" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L118" s="12" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         </is>
       </c>
       <c r="K119" s="13" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="L119" s="13" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="K120" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L120" s="12" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="K121" s="13" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L121" s="13" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         </is>
       </c>
       <c r="K122" s="12" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="L122" s="12" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="K123" s="13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L123" s="13" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="K124" s="12" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="L124" s="12" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="K125" s="13" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L125" s="13" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="K126" s="12" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L126" s="12" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="K127" s="13" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="L127" s="13" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="K128" s="12" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L128" s="12" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="K129" s="13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L129" s="13" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="K130" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L130" s="12" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="K131" s="13" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="L131" s="13" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         </is>
       </c>
       <c r="K132" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L132" s="12" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="K133" s="13" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="L133" s="13" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         </is>
       </c>
       <c r="K134" s="12" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="L134" s="12" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="K135" s="13" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L135" s="13" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         </is>
       </c>
       <c r="K136" s="12" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L136" s="12" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="K137" s="13" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="L137" s="13" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         </is>
       </c>
       <c r="K138" s="12" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="L138" s="12" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         </is>
       </c>
       <c r="K140" s="12" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="L140" s="12" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         </is>
       </c>
       <c r="K141" s="13" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="L141" s="13" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="K142" s="12" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L142" s="12" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="K143" s="13" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L143" s="13" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         </is>
       </c>
       <c r="K144" s="12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L144" s="12" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="K145" s="13" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L145" s="13" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="K146" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L146" s="12" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="K147" s="13" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="L147" s="13" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         </is>
       </c>
       <c r="K148" s="12" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L148" s="12" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="K149" s="13" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L149" s="13" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="K150" s="12" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="L150" s="12" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         </is>
       </c>
       <c r="K151" s="13" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="L151" s="13" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         </is>
       </c>
       <c r="K152" s="12" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="L152" s="12" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="K153" s="13" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="L153" s="13" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="K154" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L154" s="12" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         </is>
       </c>
       <c r="K155" s="13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L155" s="13" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="K156" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="L156" s="12" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         </is>
       </c>
       <c r="K157" s="13" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="L157" s="13" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         </is>
       </c>
       <c r="K158" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L158" s="12" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="K159" s="13" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="L159" s="13" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="K160" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L160" s="12" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="K161" s="13" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="L161" s="13" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         </is>
       </c>
       <c r="K162" s="12" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="L162" s="12" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="K163" s="13" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L163" s="13" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         </is>
       </c>
       <c r="K164" s="12" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L164" s="12" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         </is>
       </c>
       <c r="K165" s="13" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="L165" s="13" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="K167" s="13" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="L167" s="13" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="K168" s="12" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L168" s="12" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         </is>
       </c>
       <c r="K169" s="13" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="L169" s="13" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         </is>
       </c>
       <c r="K170" s="12" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="L170" s="12" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="K171" s="13" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L171" s="13" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         </is>
       </c>
       <c r="K172" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L172" s="12" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         </is>
       </c>
       <c r="K173" s="13" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="L173" s="13" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="K174" s="12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L174" s="12" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         </is>
       </c>
       <c r="K175" s="13" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L175" s="13" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="K176" s="12" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L176" s="12" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="K177" s="13" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="L177" s="13" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="K178" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L178" s="12" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="K179" s="13" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L179" s="13" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="K180" s="12" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="L180" s="12" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         </is>
       </c>
       <c r="K181" s="13" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="L181" s="13" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         </is>
       </c>
       <c r="K182" s="12" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="L182" s="12" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         </is>
       </c>
       <c r="K183" s="13" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="L183" s="13" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         </is>
       </c>
       <c r="K184" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L184" s="12" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="K185" s="13" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L185" s="13" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         </is>
       </c>
       <c r="K186" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L186" s="12" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="K187" s="13" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L187" s="13" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         </is>
       </c>
       <c r="K188" s="12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L188" s="12" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="K189" s="13" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L189" s="13" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         </is>
       </c>
       <c r="K190" s="12" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="L190" s="12" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         </is>
       </c>
       <c r="K191" s="13" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L191" s="13" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         </is>
       </c>
       <c r="K192" s="12" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L192" s="12" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         </is>
       </c>
       <c r="K193" s="13" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="L193" s="13" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="K194" s="12" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="L194" s="12" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="K195" s="13" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="L195" s="13" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         </is>
       </c>
       <c r="K196" s="12" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="L196" s="12" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="K197" s="13" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="L197" s="13" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         </is>
       </c>
       <c r="K199" s="13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L199" s="13" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         </is>
       </c>
       <c r="K200" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L200" s="12" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         </is>
       </c>
       <c r="K201" s="13" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="L201" s="13" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="K202" s="12" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L202" s="12" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         </is>
       </c>
       <c r="K203" s="13" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="L203" s="13" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="K204" s="12" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L204" s="12" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         </is>
       </c>
       <c r="K205" s="13" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="L205" s="13" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         </is>
       </c>
       <c r="K206" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L206" s="12" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         </is>
       </c>
       <c r="K207" s="13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L207" s="13" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         </is>
       </c>
       <c r="K208" s="12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L208" s="12" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         </is>
       </c>
       <c r="K209" s="13" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="L209" s="13" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="K210" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L210" s="12" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         </is>
       </c>
       <c r="K211" s="13" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L211" s="13" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         </is>
       </c>
       <c r="K212" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L212" s="12" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         </is>
       </c>
       <c r="K213" s="13" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="L213" s="13" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="K214" s="12" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="L214" s="12" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="K215" s="13" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L215" s="13" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="K216" s="12" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L216" s="12" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="K217" s="13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L217" s="13" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         </is>
       </c>
       <c r="K218" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="L218" s="12" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="K219" s="13" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="L219" s="13" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         </is>
       </c>
       <c r="K220" s="12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L220" s="12" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         </is>
       </c>
       <c r="K221" s="13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L221" s="13" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         </is>
       </c>
       <c r="K222" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L222" s="12" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         </is>
       </c>
       <c r="K223" s="13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L223" s="13" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="K224" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L224" s="12" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="K225" s="13" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="L225" s="13" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="K226" s="12" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="L226" s="12" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         </is>
       </c>
       <c r="K227" s="13" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="L227" s="13" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="K228" s="12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L228" s="12" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="K229" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L229" s="13" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         </is>
       </c>
       <c r="K230" s="12" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="L230" s="12" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         </is>
       </c>
       <c r="K231" s="13" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="L231" s="13" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="K232" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L232" s="12" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="K233" s="13" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L233" s="13" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         </is>
       </c>
       <c r="K234" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L234" s="12" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         </is>
       </c>
       <c r="K235" s="13" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L235" s="13" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         </is>
       </c>
       <c r="K236" s="12" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="L236" s="12" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         </is>
       </c>
       <c r="K237" s="13" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="L237" s="13" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         </is>
       </c>
       <c r="K238" s="12" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="L238" s="12" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         </is>
       </c>
       <c r="K239" s="13" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L239" s="13" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         </is>
       </c>
       <c r="K240" s="12" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L240" s="12" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         </is>
       </c>
       <c r="K241" s="13" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L241" s="13" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         </is>
       </c>
       <c r="K242" s="12" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L242" s="12" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         </is>
       </c>
       <c r="K243" s="13" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="L243" s="13" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         </is>
       </c>
       <c r="K245" s="13" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="L245" s="13" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         </is>
       </c>
       <c r="K246" s="12" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="L246" s="12" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         </is>
       </c>
       <c r="K247" s="13" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L247" s="13" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         </is>
       </c>
       <c r="K248" s="12" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="L248" s="12" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         </is>
       </c>
       <c r="K249" s="13" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="L249" s="13" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         </is>
       </c>
       <c r="K250" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L250" s="12" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="K251" s="13" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L251" s="13" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         </is>
       </c>
       <c r="K252" s="12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L252" s="12" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         </is>
       </c>
       <c r="K253" s="13" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="L253" s="13" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="K254" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L254" s="12" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="K255" s="13" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L255" s="13" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         </is>
       </c>
       <c r="K256" s="12" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="L256" s="12" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         </is>
       </c>
       <c r="K257" s="13" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L257" s="13" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         </is>
       </c>
       <c r="K258" s="12" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L258" s="12" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         </is>
       </c>
       <c r="K259" s="13" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L259" s="13" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         </is>
       </c>
       <c r="K260" s="12" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L260" s="12" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         </is>
       </c>
       <c r="K261" s="13" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L261" s="13" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         </is>
       </c>
       <c r="K262" s="12" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L262" s="12" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="K263" s="13" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L263" s="13" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         </is>
       </c>
       <c r="K264" s="12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L264" s="12" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         </is>
       </c>
       <c r="K265" s="13" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="L265" s="13" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         </is>
       </c>
       <c r="K266" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L266" s="12" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         </is>
       </c>
       <c r="K267" s="13" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="L267" s="13" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         </is>
       </c>
       <c r="K268" s="12" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L268" s="12" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="K269" s="13" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L269" s="13" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         </is>
       </c>
       <c r="K271" s="13" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="L271" s="13" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         </is>
       </c>
       <c r="K272" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="L272" s="12" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         </is>
       </c>
       <c r="K273" s="13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L273" s="13" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         </is>
       </c>
       <c r="K274" s="12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="L274" s="12" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="K275" s="13" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="L275" s="13" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         </is>
       </c>
       <c r="K276" s="12" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="L276" s="12" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         </is>
       </c>
       <c r="K277" s="13" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L277" s="13" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         </is>
       </c>
       <c r="K278" s="12" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L278" s="12" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="K279" s="13" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="L279" s="13" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         </is>
       </c>
       <c r="K280" s="12" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="L280" s="12" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         </is>
       </c>
       <c r="K281" s="13" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="L281" s="13" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         </is>
       </c>
       <c r="K282" s="12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L282" s="12" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         </is>
       </c>
       <c r="K283" s="13" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L283" s="13" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         </is>
       </c>
       <c r="K284" s="12" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L284" s="12" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="K285" s="13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L285" s="13" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         </is>
       </c>
       <c r="K286" s="12" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="L286" s="12" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="K287" s="13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L287" s="13" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         </is>
       </c>
       <c r="K288" s="12" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="L288" s="12" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="K289" s="13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L289" s="13" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         </is>
       </c>
       <c r="K290" s="12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="L290" s="12" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         </is>
       </c>
       <c r="K291" s="13" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="L291" s="13" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         </is>
       </c>
       <c r="K292" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L292" s="12" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="K293" s="13" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="L293" s="13" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         </is>
       </c>
       <c r="K294" s="12" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="L294" s="12" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         </is>
       </c>
       <c r="K295" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L295" s="13" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="K296" s="12" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="L296" s="12" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>870 ms</t>
+          <t>863 ms</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -19452,7 +19452,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>12 ms</t>
+          <t>9 ms</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -19479,7 +19479,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>1668 ms</t>
+          <t>1655 ms</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -19506,7 +19506,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>8008 ms</t>
+          <t>8007 ms</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>8040 ms</t>
+          <t>8020 ms</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>8044 ms</t>
+          <t>8027 ms</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -19587,7 +19587,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>7092 ms</t>
+          <t>7072 ms</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>8059 ms</t>
+          <t>8036 ms</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -19711,12 +19711,12 @@
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>508 ms</t>
+          <t>504 ms</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>6 req/s</t>
+          <t>13 req/s</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
@@ -19748,12 +19748,12 @@
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>1595 ms</t>
+          <t>1583 ms</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>8 req/s</t>
+          <t>16 req/s</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
@@ -19785,12 +19785,12 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>943 ms</t>
+          <t>935 ms</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>5 req/s</t>
+          <t>10 req/s</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -19822,12 +19822,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>1813 ms</t>
+          <t>1799 ms</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>5 req/s</t>
+          <t>10 req/s</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -19859,12 +19859,12 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>1088 ms</t>
+          <t>1079 ms</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>5 req/s</t>
+          <t>10 req/s</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -19896,12 +19896,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>725 ms</t>
+          <t>719 ms</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>3 req/s</t>
+          <t>6 req/s</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -19985,21 +19985,21 @@
         <v>100</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>32 req/s</t>
+          <t>65 req/s</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>1441.1 ms</t>
+          <t>1429.9 ms</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>89.6 KB/s</t>
+          <t>182.0 KB/s</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
@@ -20018,21 +20018,21 @@
         <v>100</v>
       </c>
       <c r="C3" s="12" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>39 req/s</t>
+          <t>72 req/s</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>1452.1 ms</t>
+          <t>1440.9 ms</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>109.2 KB/s</t>
+          <t>201.6 KB/s</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -20051,21 +20051,21 @@
         <v>100</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>31 req/s</t>
+          <t>64 req/s</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>1463.1 ms</t>
+          <t>1451.9 ms</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>86.8 KB/s</t>
+          <t>179.2 KB/s</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -20084,21 +20084,21 @@
         <v>100</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>38 req/s</t>
+          <t>71 req/s</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>1434.1 ms</t>
+          <t>1422.9 ms</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>106.4 KB/s</t>
+          <t>198.8 KB/s</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -20117,21 +20117,21 @@
         <v>100</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>30 req/s</t>
+          <t>63 req/s</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>1445.1 ms</t>
+          <t>1433.9 ms</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>84.0 KB/s</t>
+          <t>176.4 KB/s</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -20150,21 +20150,21 @@
         <v>100</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>37 req/s</t>
+          <t>70 req/s</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>1456.1 ms</t>
+          <t>1444.9 ms</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>103.6 KB/s</t>
+          <t>196.0 KB/s</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -20183,21 +20183,21 @@
         <v>100</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>29 req/s</t>
+          <t>62 req/s</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>1467.1 ms</t>
+          <t>1455.9 ms</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>81.2 KB/s</t>
+          <t>173.6 KB/s</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -20216,21 +20216,21 @@
         <v>100</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>36 req/s</t>
+          <t>69 req/s</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>1438.1 ms</t>
+          <t>1426.9 ms</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>100.8 KB/s</t>
+          <t>193.2 KB/s</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -20249,21 +20249,21 @@
         <v>100</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>28 req/s</t>
+          <t>61 req/s</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>1449.1 ms</t>
+          <t>1437.9 ms</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>78.4 KB/s</t>
+          <t>170.8 KB/s</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -20282,21 +20282,21 @@
         <v>100</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>35 req/s</t>
+          <t>68 req/s</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>1460.1 ms</t>
+          <t>1448.9 ms</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>98.0 KB/s</t>
+          <t>190.4 KB/s</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -20315,21 +20315,21 @@
         <v>100</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>27 req/s</t>
+          <t>60 req/s</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>1431.1 ms</t>
+          <t>1419.9 ms</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>75.6 KB/s</t>
+          <t>168.0 KB/s</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -20348,21 +20348,21 @@
         <v>100</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>34 req/s</t>
+          <t>67 req/s</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>1442.1 ms</t>
+          <t>1430.9 ms</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>95.2 KB/s</t>
+          <t>187.6 KB/s</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -20381,21 +20381,21 @@
         <v>100</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>26 req/s</t>
+          <t>59 req/s</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>1453.1 ms</t>
+          <t>1441.9 ms</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>72.8 KB/s</t>
+          <t>165.2 KB/s</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -20414,21 +20414,21 @@
         <v>100</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>33 req/s</t>
+          <t>66 req/s</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>1464.1 ms</t>
+          <t>1452.9 ms</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>92.4 KB/s</t>
+          <t>184.8 KB/s</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -20447,21 +20447,21 @@
         <v>100</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>25 req/s</t>
+          <t>58 req/s</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>1435.1 ms</t>
+          <t>1423.9 ms</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>70.0 KB/s</t>
+          <t>162.4 KB/s</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -20480,21 +20480,21 @@
         <v>100</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>32 req/s</t>
+          <t>65 req/s</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>1446.1 ms</t>
+          <t>1434.9 ms</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>89.6 KB/s</t>
+          <t>182.0 KB/s</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -20513,21 +20513,21 @@
         <v>100</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>39 req/s</t>
+          <t>72 req/s</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>1457.1 ms</t>
+          <t>1445.9 ms</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>109.2 KB/s</t>
+          <t>201.6 KB/s</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -20546,21 +20546,21 @@
         <v>100</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>31 req/s</t>
+          <t>64 req/s</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>1468.1 ms</t>
+          <t>1456.9 ms</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>86.8 KB/s</t>
+          <t>179.2 KB/s</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -20579,21 +20579,21 @@
         <v>100</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>38 req/s</t>
+          <t>71 req/s</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>1439.1 ms</t>
+          <t>1427.9 ms</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>106.4 KB/s</t>
+          <t>198.8 KB/s</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -20612,21 +20612,21 @@
         <v>100</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>30 req/s</t>
+          <t>63 req/s</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>1450.1 ms</t>
+          <t>1438.9 ms</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>84.0 KB/s</t>
+          <t>176.4 KB/s</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -20645,21 +20645,21 @@
         <v>100</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>37 req/s</t>
+          <t>70 req/s</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>1461.1 ms</t>
+          <t>1449.9 ms</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>103.6 KB/s</t>
+          <t>196.0 KB/s</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -20678,21 +20678,21 @@
         <v>100</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>29 req/s</t>
+          <t>62 req/s</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>1432.1 ms</t>
+          <t>1420.9 ms</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>81.2 KB/s</t>
+          <t>173.6 KB/s</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -20711,21 +20711,21 @@
         <v>100</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>36 req/s</t>
+          <t>69 req/s</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>1443.1 ms</t>
+          <t>1431.9 ms</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>100.8 KB/s</t>
+          <t>193.2 KB/s</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -20744,21 +20744,21 @@
         <v>100</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>28 req/s</t>
+          <t>61 req/s</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>1454.1 ms</t>
+          <t>1442.9 ms</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>78.4 KB/s</t>
+          <t>170.8 KB/s</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -20777,21 +20777,21 @@
         <v>100</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>35 req/s</t>
+          <t>68 req/s</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>1465.1 ms</t>
+          <t>1453.9 ms</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>98.0 KB/s</t>
+          <t>190.4 KB/s</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -20810,21 +20810,21 @@
         <v>100</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>27 req/s</t>
+          <t>60 req/s</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>1436.1 ms</t>
+          <t>1424.9 ms</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>75.6 KB/s</t>
+          <t>168.0 KB/s</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -20843,21 +20843,21 @@
         <v>100</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>34 req/s</t>
+          <t>67 req/s</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>1447.1 ms</t>
+          <t>1435.9 ms</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>95.2 KB/s</t>
+          <t>187.6 KB/s</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -20876,21 +20876,21 @@
         <v>100</v>
       </c>
       <c r="C29" s="12" t="n">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>26 req/s</t>
+          <t>59 req/s</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>1458.1 ms</t>
+          <t>1446.9 ms</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>72.8 KB/s</t>
+          <t>165.2 KB/s</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -20909,21 +20909,21 @@
         <v>100</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>33 req/s</t>
+          <t>66 req/s</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>1469.1 ms</t>
+          <t>1457.9 ms</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>92.4 KB/s</t>
+          <t>184.8 KB/s</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -20942,21 +20942,21 @@
         <v>100</v>
       </c>
       <c r="C31" s="12" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>25 req/s</t>
+          <t>58 req/s</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>1440.1 ms</t>
+          <t>1428.9 ms</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>70.0 KB/s</t>
+          <t>162.4 KB/s</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -20975,21 +20975,21 @@
         <v>100</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>32 req/s</t>
+          <t>65 req/s</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>1451.1 ms</t>
+          <t>1439.9 ms</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>89.6 KB/s</t>
+          <t>182.0 KB/s</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -21008,21 +21008,21 @@
         <v>100</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>39 req/s</t>
+          <t>72 req/s</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>1462.1 ms</t>
+          <t>1450.9 ms</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>109.2 KB/s</t>
+          <t>201.6 KB/s</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -21041,21 +21041,21 @@
         <v>100</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>31 req/s</t>
+          <t>64 req/s</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>1433.1 ms</t>
+          <t>1421.9 ms</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>86.8 KB/s</t>
+          <t>179.2 KB/s</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -21074,21 +21074,21 @@
         <v>100</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>38 req/s</t>
+          <t>71 req/s</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>1444.1 ms</t>
+          <t>1432.9 ms</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>106.4 KB/s</t>
+          <t>198.8 KB/s</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -21107,21 +21107,21 @@
         <v>100</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>30 req/s</t>
+          <t>63 req/s</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>1455.1 ms</t>
+          <t>1443.9 ms</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>84.0 KB/s</t>
+          <t>176.4 KB/s</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -21140,21 +21140,21 @@
         <v>100</v>
       </c>
       <c r="C37" s="12" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>37 req/s</t>
+          <t>70 req/s</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>1466.1 ms</t>
+          <t>1454.9 ms</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>103.6 KB/s</t>
+          <t>196.0 KB/s</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -21173,21 +21173,21 @@
         <v>100</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>29 req/s</t>
+          <t>62 req/s</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>1437.1 ms</t>
+          <t>1425.9 ms</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>81.2 KB/s</t>
+          <t>173.6 KB/s</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -21206,21 +21206,21 @@
         <v>100</v>
       </c>
       <c r="C39" s="12" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>36 req/s</t>
+          <t>69 req/s</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>1448.1 ms</t>
+          <t>1436.9 ms</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>100.8 KB/s</t>
+          <t>193.2 KB/s</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -21239,21 +21239,21 @@
         <v>100</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>28 req/s</t>
+          <t>61 req/s</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>1459.1 ms</t>
+          <t>1447.9 ms</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>78.4 KB/s</t>
+          <t>170.8 KB/s</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -21272,21 +21272,21 @@
         <v>100</v>
       </c>
       <c r="C41" s="12" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>35 req/s</t>
+          <t>68 req/s</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>1430.1 ms</t>
+          <t>1418.9 ms</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>98.0 KB/s</t>
+          <t>190.4 KB/s</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -21305,21 +21305,21 @@
         <v>100</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>27 req/s</t>
+          <t>60 req/s</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>1441.1 ms</t>
+          <t>1429.9 ms</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>75.6 KB/s</t>
+          <t>168.0 KB/s</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -21338,21 +21338,21 @@
         <v>100</v>
       </c>
       <c r="C43" s="12" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>34 req/s</t>
+          <t>67 req/s</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>1452.1 ms</t>
+          <t>1440.9 ms</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>95.2 KB/s</t>
+          <t>187.6 KB/s</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -21371,21 +21371,21 @@
         <v>100</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>26 req/s</t>
+          <t>59 req/s</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>1463.1 ms</t>
+          <t>1451.9 ms</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>72.8 KB/s</t>
+          <t>165.2 KB/s</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -21404,21 +21404,21 @@
         <v>100</v>
       </c>
       <c r="C45" s="12" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>33 req/s</t>
+          <t>66 req/s</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>1434.1 ms</t>
+          <t>1422.9 ms</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>92.4 KB/s</t>
+          <t>184.8 KB/s</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -21437,21 +21437,21 @@
         <v>100</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>25 req/s</t>
+          <t>58 req/s</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>1445.1 ms</t>
+          <t>1433.9 ms</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>70.0 KB/s</t>
+          <t>162.4 KB/s</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -21470,21 +21470,21 @@
         <v>100</v>
       </c>
       <c r="C47" s="12" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>32 req/s</t>
+          <t>65 req/s</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>1456.1 ms</t>
+          <t>1444.9 ms</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>89.6 KB/s</t>
+          <t>182.0 KB/s</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -21503,21 +21503,21 @@
         <v>100</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>39 req/s</t>
+          <t>72 req/s</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>1467.1 ms</t>
+          <t>1455.9 ms</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>109.2 KB/s</t>
+          <t>201.6 KB/s</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -21536,21 +21536,21 @@
         <v>100</v>
       </c>
       <c r="C49" s="12" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>31 req/s</t>
+          <t>64 req/s</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>1438.1 ms</t>
+          <t>1426.9 ms</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>86.8 KB/s</t>
+          <t>179.2 KB/s</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -21569,21 +21569,21 @@
         <v>100</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>38 req/s</t>
+          <t>71 req/s</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>1449.1 ms</t>
+          <t>1437.9 ms</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>106.4 KB/s</t>
+          <t>198.8 KB/s</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -21602,21 +21602,21 @@
         <v>100</v>
       </c>
       <c r="C51" s="12" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>30 req/s</t>
+          <t>63 req/s</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>1460.1 ms</t>
+          <t>1448.9 ms</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>84.0 KB/s</t>
+          <t>176.4 KB/s</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -21635,21 +21635,21 @@
         <v>100</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>37 req/s</t>
+          <t>70 req/s</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>1431.1 ms</t>
+          <t>1419.9 ms</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>103.6 KB/s</t>
+          <t>196.0 KB/s</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -21668,21 +21668,21 @@
         <v>100</v>
       </c>
       <c r="C53" s="12" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>29 req/s</t>
+          <t>62 req/s</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>1442.1 ms</t>
+          <t>1430.9 ms</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>81.2 KB/s</t>
+          <t>173.6 KB/s</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -21701,21 +21701,21 @@
         <v>100</v>
       </c>
       <c r="C54" s="13" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>36 req/s</t>
+          <t>69 req/s</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>1453.1 ms</t>
+          <t>1441.9 ms</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>100.8 KB/s</t>
+          <t>193.2 KB/s</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -21734,21 +21734,21 @@
         <v>100</v>
       </c>
       <c r="C55" s="12" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>28 req/s</t>
+          <t>61 req/s</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>1464.1 ms</t>
+          <t>1452.9 ms</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>78.4 KB/s</t>
+          <t>170.8 KB/s</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
@@ -21767,21 +21767,21 @@
         <v>100</v>
       </c>
       <c r="C56" s="13" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>35 req/s</t>
+          <t>68 req/s</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>1435.1 ms</t>
+          <t>1423.9 ms</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>98.0 KB/s</t>
+          <t>190.4 KB/s</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -21800,21 +21800,21 @@
         <v>100</v>
       </c>
       <c r="C57" s="12" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>27 req/s</t>
+          <t>60 req/s</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>1446.1 ms</t>
+          <t>1434.9 ms</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>75.6 KB/s</t>
+          <t>168.0 KB/s</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -21833,21 +21833,21 @@
         <v>100</v>
       </c>
       <c r="C58" s="13" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>34 req/s</t>
+          <t>67 req/s</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>1457.1 ms</t>
+          <t>1445.9 ms</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>95.2 KB/s</t>
+          <t>187.6 KB/s</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -21866,21 +21866,21 @@
         <v>100</v>
       </c>
       <c r="C59" s="12" t="n">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>26 req/s</t>
+          <t>59 req/s</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>1468.1 ms</t>
+          <t>1456.9 ms</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>72.8 KB/s</t>
+          <t>165.2 KB/s</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
@@ -21899,21 +21899,21 @@
         <v>100</v>
       </c>
       <c r="C60" s="13" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>33 req/s</t>
+          <t>66 req/s</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>1439.1 ms</t>
+          <t>1427.9 ms</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>92.4 KB/s</t>
+          <t>184.8 KB/s</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -21932,21 +21932,21 @@
         <v>100</v>
       </c>
       <c r="C61" s="12" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>25 req/s</t>
+          <t>58 req/s</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>1450.1 ms</t>
+          <t>1438.9 ms</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>70.0 KB/s</t>
+          <t>162.4 KB/s</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
